--- a/reports/FR-03_boundary_test_cases.xlsx
+++ b/reports/FR-03_boundary_test_cases.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Test Cases'!$A$1:$I$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variables!$A$1:$E$8</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -669,11 +669,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1217,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -1285,7 +1285,7 @@
       <c r="H2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>124</v>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       <c r="H3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="7"/>
+      <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -1341,7 +1341,7 @@
       <c r="H4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="7"/>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -1368,7 +1368,7 @@
       <c r="H5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="7"/>
+      <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1380,7 +1380,7 @@
       <c r="C6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1395,7 +1395,7 @@
       <c r="H6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="7"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -1500,7 +1500,7 @@
       <c r="G10" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>148</v>
       </c>
       <c r="I10" s="5"/>
@@ -1527,7 +1527,7 @@
       <c r="G11" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1579,7 +1579,7 @@
       <c r="G13" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="8" t="s">
         <v>148</v>
       </c>
       <c r="I13" s="5"/>
@@ -1606,7 +1606,7 @@
       <c r="G14" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H14" s="7"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1658,7 +1658,7 @@
       <c r="G16" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>148</v>
       </c>
       <c r="I16" s="5"/>
@@ -1685,7 +1685,7 @@
       <c r="G17" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="8"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1916,7 +1916,7 @@
       <c r="H26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       <c r="H27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I27" s="7"/>
+      <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -1972,7 +1972,7 @@
       <c r="H28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="8" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       <c r="H29" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="7"/>
+      <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -2028,7 +2028,7 @@
       <c r="H30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I30" s="7"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
@@ -2052,7 +2052,7 @@
       <c r="G31" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="8" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       <c r="G32" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H32" s="7"/>
+      <c r="H32" s="8"/>
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
@@ -2102,7 +2102,7 @@
       <c r="G33" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H33" s="7"/>
+      <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
@@ -2126,7 +2126,7 @@
       <c r="G34" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H34" s="7"/>
+      <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
@@ -2150,7 +2150,23 @@
       <c r="G35" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H35" s="7"/>
+      <c r="H35" s="8"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G37"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G38"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G39"/>
+      <c r="H39"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G40"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G41"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I30"/>
